--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,260 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>110</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
@@ -869,34 +869,34 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
         <v>1.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="R2" t="n">
         <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -884,7 +884,7 @@
         <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P2" t="n">
         <v>1.36</v>
@@ -893,7 +893,7 @@
         <v>1.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>1.86</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,31 +857,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O2" t="n">
         <v>1.11</v>
@@ -890,25 +890,25 @@
         <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -923,19 +923,19 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
         <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -950,7 +950,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -965,112 +965,112 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -860,19 +860,19 @@
         <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>55</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.21</v>
@@ -881,196 +881,196 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.37</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.36</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.18</v>
+        <v>2.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.6</v>
+        <v>1.27</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.6</v>
+        <v>1.05</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>14</v>
+        <v>1.15</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>21</v>
+        <v>1.15</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -860,19 +860,19 @@
         <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.21</v>
@@ -887,7 +887,7 @@
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
         <v>1.44</v>
@@ -908,7 +908,7 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -965,58 +965,58 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="BF2" t="n">
         <v>3.35</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -860,13 +860,13 @@
         <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
@@ -875,40 +875,40 @@
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U2" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -932,7 +932,7 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -944,10 +944,10 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>970</v>
@@ -965,112 +965,112 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.99</v>
+        <v>1.56</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,70 +857,70 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G2" t="n">
         <v>1.86</v>
       </c>
       <c r="H2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.2</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.12</v>
-      </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.76</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
         <v>2.16</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -932,7 +932,7 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -944,7 +944,7 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -956,7 +956,7 @@
         <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
         <v>970</v>
@@ -965,112 +965,112 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.69</v>
+        <v>2.42</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.19</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.06</v>
+        <v>1.84</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,498 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>CD Cuenca Juniors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>LDU de Portoviejo</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
         <v>1.03</v>
       </c>
-      <c r="N2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI2" t="n">
         <v>2.34</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BJ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK2" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.56</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.84</v>
+        <v>26</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.44</v>
+        <v>6.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.05</v>
+        <v>55</v>
       </c>
       <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-07-09 04:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CA3" t="n">
         <v>0</v>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-07-09 02:26:20</t>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,205 +857,205 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
         <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
         <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB2" t="n">
         <v>7.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>13</v>
       </c>
-      <c r="AH2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11</v>
-      </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>19</v>
       </c>
-      <c r="BA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>17</v>
-      </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>130</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO2" t="n">
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU2" t="n">
         <v>6.6</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
@@ -1144,25 +1144,25 @@
         <v>2.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
         <v>1.51</v>
       </c>
       <c r="U3" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
@@ -1198,7 +1198,7 @@
         <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
         <v>34</v>
@@ -1213,82 +1213,82 @@
         <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
         <v>4.8</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY3" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
         <v>5.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.35</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,64 +857,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H2" t="n">
         <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
         <v>48</v>
@@ -923,10 +923,10 @@
         <v>210</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
@@ -938,19 +938,19 @@
         <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -959,76 +959,76 @@
         <v>220</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
         <v>190</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
         <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,22 +1037,22 @@
         <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BT2" t="n">
         <v>9.4</v>
@@ -1064,7 +1064,7 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>3.8</v>
@@ -1126,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.27</v>
@@ -1135,43 +1135,43 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
         <v>2.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1198,7 +1198,7 @@
         <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
         <v>34</v>
@@ -1210,121 +1210,121 @@
         <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.8</v>
+        <v>2.12</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>21</v>
       </c>
-      <c r="BA2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1043,44 +1043,44 @@
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
@@ -1135,28 +1135,28 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
         <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
@@ -1168,13 +1168,13 @@
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
@@ -1186,7 +1186,7 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1201,7 +1201,7 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
         <v>970</v>
@@ -1213,100 +1213,100 @@
         <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AW3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AY3" t="n">
         <v>3.45</v>
       </c>
-      <c r="AX3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>2.78</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>2.92</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BF3" t="n">
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.58</v>
@@ -881,154 +881,154 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.6</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.68</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AE2" t="n">
         <v>160</v>
       </c>
       <c r="AF2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
         <v>310</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="AP2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="n">
         <v>2.82</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,13 +1037,13 @@
         <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO2" t="n">
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
         <v>10.5</v>
@@ -1055,10 +1055,10 @@
         <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:36</t>
+          <t>2026-07-09 13:41:30</t>
         </is>
       </c>
     </row>
@@ -1111,73 +1111,73 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>4.1</v>
       </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
         <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1186,22 +1186,22 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
         <v>970</v>
@@ -1210,7 +1210,7 @@
         <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN3" t="n">
         <v>970</v>
@@ -1219,112 +1219,112 @@
         <v>55</v>
       </c>
       <c r="AP3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX3" t="n">
         <v>3</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AY3" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="BN3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BO3" t="n">
         <v>5</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:36</t>
+          <t>2026-07-09 13:41:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,76 +857,76 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2" t="n">
         <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AB2" t="n">
         <v>6.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>44</v>
@@ -935,7 +935,7 @@
         <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -947,37 +947,37 @@
         <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -986,43 +986,43 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
         <v>9</v>
       </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>21</v>
-      </c>
       <c r="BE2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2" t="n">
         <v>13</v>
@@ -1037,10 +1037,10 @@
         <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
         <v>14</v>
@@ -1055,7 +1055,7 @@
         <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU2" t="n">
         <v>7.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="X3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
         <v>26</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AE3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR3" t="n">
         <v>32</v>
       </c>
-      <c r="AA3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AS3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC3" t="n">
         <v>14</v>
       </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BD3" t="n">
-        <v>2.46</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.7</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="BN3" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.56</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
         <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AF2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG2" t="n">
         <v>9.4</v>
       </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AM2" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>190</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>16</v>
       </c>
-      <c r="BG2" t="n">
-        <v>10</v>
-      </c>
       <c r="BH2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -1141,190 +1141,190 @@
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y3" t="n">
         <v>25</v>
       </c>
-      <c r="Y3" t="n">
-        <v>28</v>
-      </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
         <v>150</v>
       </c>
       <c r="AB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF3" t="n">
         <v>14</v>
       </c>
-      <c r="AC3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15</v>
-      </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
         <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="AR3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW3" t="n">
         <v>32</v>
       </c>
-      <c r="AS3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>29</v>
-      </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
         <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
         <v>4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CD Cuenca Juniors</t>
+          <t>Nacional Potosi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LDU de Portoviejo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
+      <c r="Y2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z2" t="n">
         <v>32</v>
       </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="AA2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU2" t="n">
         <v>6.4</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W2" t="n">
-        <v>5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>370</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>350</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,261 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Nacional Potosi</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-09.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>100</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>160</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3.75</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AZ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC2" t="n">
         <v>50</v>
       </c>
-      <c r="AF2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="BD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
